--- a/assets/excel/3-statement-model-nestle-india.xlsx
+++ b/assets/excel/3-statement-model-nestle-india.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANVAY PORTFOLIO (WEBSITE)\Financial Modeling\CORE MODELS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anvay Document\ANVAY-PORTFOLIO-WEBSITE\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE62120-D891-4811-A4B9-B51574C7A00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E230EE-7A5F-4626-987F-F9CE781C6997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="657" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Assumptions!$A$1:$E$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Cash Flow'!$A$1:$P$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">Dashboard!$A$1:$Q$81</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">Dashboard!$A$1:$Q$83</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Income Statement'!$A$1:$P$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -924,7 +924,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="218">
   <si>
     <t>A.  REVENUE DRIVERS</t>
   </si>
@@ -1572,13 +1572,22 @@
   </si>
   <si>
     <t>Key risks include rising raw material costs (coffee, cocoa, wheat), slower urban demand, and increasing competition from regional brands in noodles. There is also some uncertainty due to leadership change and potential conflicts with quick commerce channels.</t>
+  </si>
+  <si>
+    <t>Supporting Inputs</t>
+  </si>
+  <si>
+    <t>EBTDA MARGIN</t>
+  </si>
+  <si>
+    <t>Reve Grow</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
@@ -1588,8 +1597,9 @@
     <numFmt numFmtId="170" formatCode="yyyy&quot;E&quot;"/>
     <numFmt numFmtId="171" formatCode="\₹\ #,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="172" formatCode="0.00%;\(0.00%\);\-"/>
+    <numFmt numFmtId="173" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1868,6 +1878,27 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -2003,7 +2034,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -2264,12 +2295,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -2709,9 +2749,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="168" fontId="28" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2754,20 +2791,11 @@
     <xf numFmtId="1" fontId="22" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="6"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="20" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="10"/>
@@ -2775,29 +2803,11 @@
     <xf numFmtId="0" fontId="38" fillId="20" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="10"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
@@ -2829,6 +2839,33 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2852,6 +2889,33 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8969,13 +9033,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>142395</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>60034</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>156112</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9005,13 +9069,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>462665</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>107757</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>68341</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9041,13 +9105,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>150091</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>153939</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>154786</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>86955</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9077,13 +9141,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>382401</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>142259</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>61576</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9327,11 +9391,11 @@
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2" s="10"/>
-      <c r="N2" s="150" t="s">
+      <c r="N2" s="165" t="s">
         <v>173</v>
       </c>
-      <c r="O2" s="150"/>
-      <c r="P2" s="150"/>
+      <c r="O2" s="165"/>
+      <c r="P2" s="165"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F3" s="3"/>
@@ -9344,10 +9408,10 @@
       <c r="N3" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="O3" s="151">
+      <c r="O3" s="153">
         <v>1</v>
       </c>
-      <c r="P3" s="152"/>
+      <c r="P3" s="154"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F4" s="3"/>
@@ -9360,10 +9424,10 @@
       <c r="N4" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="O4" s="151">
+      <c r="O4" s="187">
         <v>46117</v>
       </c>
-      <c r="P4" s="152"/>
+      <c r="P4" s="188"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F5" s="3"/>
@@ -9376,10 +9440,10 @@
       <c r="N5" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="O5" s="151" t="s">
+      <c r="O5" s="153" t="s">
         <v>177</v>
       </c>
-      <c r="P5" s="152"/>
+      <c r="P5" s="154"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F6" s="3"/>
@@ -9394,10 +9458,10 @@
       <c r="N6" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="O6" s="153" t="s">
+      <c r="O6" s="166" t="s">
         <v>179</v>
       </c>
-      <c r="P6" s="154"/>
+      <c r="P6" s="167"/>
     </row>
     <row r="7" spans="1:16" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F7" s="3"/>
@@ -9429,24 +9493,24 @@
     </row>
     <row r="9" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:16" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B10" s="157" t="s">
+      <c r="B10" s="168" t="s">
         <v>180</v>
       </c>
-      <c r="C10" s="157"/>
-      <c r="E10" s="163" t="s">
+      <c r="C10" s="168"/>
+      <c r="E10" s="149" t="s">
         <v>198</v>
       </c>
-      <c r="F10" s="163"/>
-      <c r="G10" s="163"/>
-      <c r="H10" s="163"/>
-      <c r="I10" s="163"/>
-      <c r="K10" s="164" t="s">
+      <c r="F10" s="149"/>
+      <c r="G10" s="149"/>
+      <c r="H10" s="149"/>
+      <c r="I10" s="149"/>
+      <c r="K10" s="150" t="s">
         <v>199</v>
       </c>
-      <c r="L10" s="164"/>
-      <c r="M10" s="164"/>
-      <c r="N10" s="164"/>
-      <c r="O10" s="164"/>
+      <c r="L10" s="150"/>
+      <c r="M10" s="150"/>
+      <c r="N10" s="150"/>
+      <c r="O10" s="150"/>
     </row>
     <row r="11" spans="1:16" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11"/>
@@ -9463,10 +9527,10 @@
       <c r="O11"/>
     </row>
     <row r="12" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="155" t="s">
+      <c r="B12" s="151" t="s">
         <v>181</v>
       </c>
-      <c r="C12" s="156"/>
+      <c r="C12" s="152"/>
       <c r="E12"/>
       <c r="F12" t="s">
         <v>172</v>
@@ -9474,81 +9538,81 @@
       <c r="G12"/>
       <c r="H12"/>
       <c r="I12"/>
-      <c r="K12" s="158" t="s">
+      <c r="K12" s="169" t="s">
         <v>188</v>
       </c>
-      <c r="L12" s="159"/>
-      <c r="M12" s="160" t="s">
+      <c r="L12" s="170"/>
+      <c r="M12" s="171" t="s">
         <v>191</v>
       </c>
-      <c r="N12" s="161"/>
-      <c r="O12" s="162"/>
+      <c r="N12" s="172"/>
+      <c r="O12" s="173"/>
     </row>
     <row r="13" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="155" t="s">
+      <c r="B13" s="151" t="s">
         <v>182</v>
       </c>
-      <c r="C13" s="156"/>
+      <c r="C13" s="152"/>
       <c r="E13"/>
       <c r="F13" s="6"/>
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13"/>
-      <c r="K13" s="165" t="s">
+      <c r="K13" s="155" t="s">
         <v>189</v>
       </c>
-      <c r="L13" s="166"/>
-      <c r="M13" s="169" t="s">
+      <c r="L13" s="156"/>
+      <c r="M13" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="N13" s="170"/>
-      <c r="O13" s="171"/>
+      <c r="N13" s="160"/>
+      <c r="O13" s="161"/>
     </row>
     <row r="14" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="155" t="s">
+      <c r="B14" s="151" t="s">
         <v>183</v>
       </c>
-      <c r="C14" s="156"/>
+      <c r="C14" s="152"/>
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14"/>
       <c r="H14"/>
       <c r="I14"/>
-      <c r="K14" s="165" t="s">
+      <c r="K14" s="155" t="s">
         <v>194</v>
       </c>
-      <c r="L14" s="166"/>
-      <c r="M14" s="169" t="s">
+      <c r="L14" s="156"/>
+      <c r="M14" s="159" t="s">
         <v>193</v>
       </c>
-      <c r="N14" s="170"/>
-      <c r="O14" s="171"/>
+      <c r="N14" s="160"/>
+      <c r="O14" s="161"/>
     </row>
     <row r="15" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="155" t="s">
+      <c r="B15" s="151" t="s">
         <v>184</v>
       </c>
-      <c r="C15" s="156"/>
+      <c r="C15" s="152"/>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15"/>
       <c r="I15"/>
-      <c r="K15" s="167" t="s">
+      <c r="K15" s="157" t="s">
         <v>190</v>
       </c>
-      <c r="L15" s="168"/>
-      <c r="M15" s="172" t="s">
+      <c r="L15" s="158"/>
+      <c r="M15" s="162" t="s">
         <v>195</v>
       </c>
-      <c r="N15" s="173"/>
-      <c r="O15" s="174"/>
+      <c r="N15" s="163"/>
+      <c r="O15" s="164"/>
     </row>
     <row r="16" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="155" t="s">
+      <c r="B16" s="151" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="156"/>
+      <c r="C16" s="152"/>
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16"/>
@@ -9558,10 +9622,10 @@
       <c r="O16" s="5"/>
     </row>
     <row r="17" spans="2:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="155" t="s">
+      <c r="B17" s="151" t="s">
         <v>186</v>
       </c>
-      <c r="C17" s="156"/>
+      <c r="C17" s="152"/>
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17"/>
@@ -9569,10 +9633,10 @@
       <c r="I17"/>
     </row>
     <row r="18" spans="2:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="155" t="s">
+      <c r="B18" s="151" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="156"/>
+      <c r="C18" s="152"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -9588,13 +9652,13 @@
       <c r="G19"/>
     </row>
     <row r="20" spans="2:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="163" t="s">
+      <c r="B20" s="149" t="s">
         <v>200</v>
       </c>
-      <c r="C20" s="163"/>
-      <c r="D20" s="163"/>
-      <c r="E20" s="163"/>
-      <c r="F20" s="163"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="149"/>
+      <c r="F20" s="149"/>
       <c r="G20"/>
     </row>
     <row r="21" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9662,8 +9726,15 @@
     <row r="33" s="2" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" s="2" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="MAslX1h5t6XGK6Z5H7Cs+iH280RSqkEtjxD0fl9MlbgBaI9Q/GevFVuHo7dL+OOVkd2x7I4Fkvk7mUcOPAUEUg==" saltValue="Tkq4TSGyPIKsha5s05SrWQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="24">
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:O12"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="E10:I10"/>
     <mergeCell ref="K10:O10"/>
@@ -9680,14 +9751,6 @@
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="M14:O14"/>
     <mergeCell ref="M15:O15"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:O12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B12:C12" location="COVER!A1" display="1.  Cover Page" xr:uid="{C3FFABC6-12B2-4A48-8C61-D8BAB7B99ADA}"/>
@@ -9722,20 +9785,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="177" t="s">
+      <c r="B1" s="176" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
     </row>
     <row r="3" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="178" t="s">
+      <c r="B3" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
       <c r="G3" s="23"/>
     </row>
     <row r="4" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -9798,12 +9861,12 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="178" t="s">
+      <c r="B9" s="177" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="178"/>
-      <c r="D9" s="178"/>
-      <c r="E9" s="178"/>
+      <c r="C9" s="177"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="177"/>
     </row>
     <row r="10" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="24" t="s">
@@ -10017,12 +10080,12 @@
       </c>
     </row>
     <row r="33" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="178" t="s">
+      <c r="B33" s="177" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="178"/>
-      <c r="D33" s="178"/>
-      <c r="E33" s="178"/>
+      <c r="C33" s="177"/>
+      <c r="D33" s="177"/>
+      <c r="E33" s="177"/>
     </row>
     <row r="34" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="24" t="s">
@@ -10175,12 +10238,12 @@
       <c r="U45" s="2"/>
     </row>
     <row r="46" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="178" t="s">
+      <c r="B46" s="177" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="178"/>
-      <c r="D46" s="178"/>
-      <c r="E46" s="178"/>
+      <c r="C46" s="177"/>
+      <c r="D46" s="177"/>
+      <c r="E46" s="177"/>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
@@ -10193,11 +10256,11 @@
       <c r="B47" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="176" t="s">
+      <c r="C47" s="175" t="s">
         <v>210</v>
       </c>
-      <c r="D47" s="176"/>
-      <c r="E47" s="176"/>
+      <c r="D47" s="175"/>
+      <c r="E47" s="175"/>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
@@ -10210,11 +10273,11 @@
       <c r="B48" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="175" t="s">
+      <c r="C48" s="174" t="s">
         <v>211</v>
       </c>
-      <c r="D48" s="175"/>
-      <c r="E48" s="175"/>
+      <c r="D48" s="174"/>
+      <c r="E48" s="174"/>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
@@ -10227,11 +10290,11 @@
       <c r="B49" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="176" t="s">
+      <c r="C49" s="175" t="s">
         <v>212</v>
       </c>
-      <c r="D49" s="176"/>
-      <c r="E49" s="176"/>
+      <c r="D49" s="175"/>
+      <c r="E49" s="175"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
@@ -10244,11 +10307,11 @@
       <c r="B50" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C50" s="175" t="s">
+      <c r="C50" s="174" t="s">
         <v>213</v>
       </c>
-      <c r="D50" s="175"/>
-      <c r="E50" s="175"/>
+      <c r="D50" s="174"/>
+      <c r="E50" s="174"/>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
@@ -10261,14 +10324,14 @@
       <c r="B51" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="C51" s="176" t="s">
+      <c r="C51" s="175" t="s">
         <v>214</v>
       </c>
-      <c r="D51" s="176"/>
-      <c r="E51" s="176"/>
+      <c r="D51" s="175"/>
+      <c r="E51" s="175"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ejSd/L2WCKdDZN9tKurcMZ8cvajdO0PoOAe9S9VRpYZgm6KutB7UKrDwlfdLtYc97HSwkR4KCQ7x8QXV8QuG1Q==" saltValue="l61UsdLO+K3CwDqBhsrehA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="btk0e6SVhRA7sfinWwGdN3VUCE9wxnbs60p4s+RweUP3QlIdpvuICzRzEHwVO3nQN1v6UIt7VFJGi4LZ/K4yZw==" saltValue="bo7zv8VMBttWtlDZjbqTlQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="10">
     <mergeCell ref="C48:E48"/>
     <mergeCell ref="C49:E49"/>
@@ -10310,44 +10373,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:25" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="177" t="s">
+      <c r="B1" s="176" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-      <c r="J1" s="177"/>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
-      <c r="N1" s="177"/>
-      <c r="O1" s="177"/>
-      <c r="P1" s="177"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="176"/>
+      <c r="N1" s="176"/>
+      <c r="O1" s="176"/>
+      <c r="P1" s="176"/>
     </row>
     <row r="2" spans="2:25" s="2" customFormat="1" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="179" t="s">
+      <c r="C3" s="178" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="179"/>
-      <c r="I3" s="179"/>
-      <c r="J3" s="179"/>
-      <c r="K3" s="179"/>
-      <c r="L3" s="179"/>
-      <c r="M3" s="179"/>
-      <c r="N3" s="180" t="s">
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="178"/>
+      <c r="I3" s="178"/>
+      <c r="J3" s="178"/>
+      <c r="K3" s="178"/>
+      <c r="L3" s="178"/>
+      <c r="M3" s="178"/>
+      <c r="N3" s="179" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="180"/>
-      <c r="P3" s="180"/>
+      <c r="O3" s="179"/>
+      <c r="P3" s="179"/>
     </row>
     <row r="4" spans="2:25" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="46" t="s">
@@ -10525,7 +10588,7 @@
         <v>#N/A</v>
       </c>
       <c r="N8" s="74">
-        <f>Assumptions!C7</f>
+        <f>Dashboard!K31</f>
         <v>0.1</v>
       </c>
       <c r="O8" s="74">
@@ -11006,7 +11069,7 @@
         <v>0.23616473616473616</v>
       </c>
       <c r="N17" s="80">
-        <f>Assumptions!C21</f>
+        <f>Dashboard!K30</f>
         <v>0.215</v>
       </c>
       <c r="O17" s="80">
@@ -11924,7 +11987,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kaZIHOROFeKJbQ0YkJnMtt8UT+7hGN7WBbHy+/gEhIE0LLgLv0yjHQWE2j33d5s5IyXWXIH6SGIdgb43hEGmmQ==" saltValue="j1TMUQx1QQTqjaTpK29eDw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wpeOLSTcGnTWoFQHLdmzwMFhX0F3EUaJVrOgByjZo8F5dQpftjtfIg3CPwggV9OosibB7dECXn6BaIVnZ9ZvBQ==" saltValue="wZ9dNwhKt6XyPUfv5FhS5Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="3">
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="C3:M3"/>
@@ -11955,44 +12018,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="177" t="s">
+      <c r="B1" s="176" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-      <c r="J1" s="177"/>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
-      <c r="N1" s="177"/>
-      <c r="O1" s="177"/>
-      <c r="P1" s="177"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="176"/>
+      <c r="N1" s="176"/>
+      <c r="O1" s="176"/>
+      <c r="P1" s="176"/>
     </row>
     <row r="2" spans="2:16" s="2" customFormat="1" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="179" t="s">
+      <c r="C3" s="178" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="179"/>
-      <c r="I3" s="179"/>
-      <c r="J3" s="179"/>
-      <c r="K3" s="179"/>
-      <c r="L3" s="179"/>
-      <c r="M3" s="179"/>
-      <c r="N3" s="180" t="s">
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="178"/>
+      <c r="I3" s="178"/>
+      <c r="J3" s="178"/>
+      <c r="K3" s="178"/>
+      <c r="L3" s="178"/>
+      <c r="M3" s="178"/>
+      <c r="N3" s="179" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="180"/>
-      <c r="P3" s="180"/>
+      <c r="O3" s="179"/>
+      <c r="P3" s="179"/>
     </row>
     <row r="4" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="46" t="s">
@@ -13157,44 +13220,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="177" t="s">
+      <c r="B1" s="176" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-      <c r="J1" s="177"/>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
-      <c r="N1" s="177"/>
-      <c r="O1" s="177"/>
-      <c r="P1" s="177"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="176"/>
+      <c r="N1" s="176"/>
+      <c r="O1" s="176"/>
+      <c r="P1" s="176"/>
     </row>
     <row r="2" spans="2:16" s="2" customFormat="1" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="179" t="s">
+      <c r="C3" s="178" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="179"/>
-      <c r="I3" s="179"/>
-      <c r="J3" s="179"/>
-      <c r="K3" s="179"/>
-      <c r="L3" s="179"/>
-      <c r="M3" s="179"/>
-      <c r="N3" s="180" t="s">
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="178"/>
+      <c r="I3" s="178"/>
+      <c r="J3" s="178"/>
+      <c r="K3" s="178"/>
+      <c r="L3" s="178"/>
+      <c r="M3" s="178"/>
+      <c r="N3" s="179" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="180"/>
-      <c r="P3" s="180"/>
+      <c r="O3" s="179"/>
+      <c r="P3" s="179"/>
     </row>
     <row r="4" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="46" t="s">
@@ -14706,44 +14769,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="177" t="s">
+      <c r="B1" s="176" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-      <c r="J1" s="177"/>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
-      <c r="N1" s="177"/>
-      <c r="O1" s="177"/>
-      <c r="P1" s="177"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="176"/>
+      <c r="N1" s="176"/>
+      <c r="O1" s="176"/>
+      <c r="P1" s="176"/>
     </row>
     <row r="2" spans="2:16" s="2" customFormat="1" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="179" t="s">
+      <c r="C3" s="178" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="179"/>
-      <c r="I3" s="179"/>
-      <c r="J3" s="179"/>
-      <c r="K3" s="179"/>
-      <c r="L3" s="179"/>
-      <c r="M3" s="179"/>
-      <c r="N3" s="180" t="s">
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="178"/>
+      <c r="I3" s="178"/>
+      <c r="J3" s="178"/>
+      <c r="K3" s="178"/>
+      <c r="L3" s="178"/>
+      <c r="M3" s="178"/>
+      <c r="N3" s="179" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="180"/>
-      <c r="P3" s="180"/>
+      <c r="O3" s="179"/>
+      <c r="P3" s="179"/>
     </row>
     <row r="4" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="46" t="s">
@@ -15996,7 +16059,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:R34"/>
+  <dimension ref="B1:R36"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="2" customWidth="1"/>
@@ -16010,24 +16073,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="177" t="s">
+      <c r="B1" s="176" t="s">
         <v>137</v>
       </c>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-      <c r="J1" s="177"/>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
-      <c r="N1" s="177"/>
-      <c r="O1" s="177"/>
-      <c r="P1" s="177"/>
-      <c r="Q1" s="177"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="176"/>
+      <c r="N1" s="176"/>
+      <c r="O1" s="176"/>
+      <c r="P1" s="176"/>
+      <c r="Q1" s="176"/>
     </row>
     <row r="2" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -16100,15 +16163,15 @@
         <f>'Balance Sheet'!M4</f>
         <v>45664</v>
       </c>
-      <c r="O4" s="136">
+      <c r="O4" s="135">
         <f>'Balance Sheet'!N4</f>
         <v>46030</v>
       </c>
-      <c r="P4" s="136">
+      <c r="P4" s="135">
         <f>'Balance Sheet'!O4</f>
         <v>46396</v>
       </c>
-      <c r="Q4" s="136">
+      <c r="Q4" s="135">
         <f>'Balance Sheet'!P4</f>
         <v>46762</v>
       </c>
@@ -16120,59 +16183,59 @@
       <c r="C5" s="129" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="137">
+      <c r="D5" s="136">
         <f>'Income Statement'!C7</f>
         <v>9141</v>
       </c>
-      <c r="E5" s="137">
+      <c r="E5" s="136">
         <f>'Income Statement'!D7</f>
         <v>10010</v>
       </c>
-      <c r="F5" s="137">
+      <c r="F5" s="136">
         <f>'Income Statement'!E7</f>
         <v>11292</v>
       </c>
-      <c r="G5" s="137">
+      <c r="G5" s="136">
         <f>'Income Statement'!F7</f>
         <v>12369</v>
       </c>
-      <c r="H5" s="137">
+      <c r="H5" s="136">
         <f>'Income Statement'!G7</f>
         <v>13350</v>
       </c>
-      <c r="I5" s="137">
+      <c r="I5" s="136">
         <f>'Income Statement'!H7</f>
         <v>14741</v>
       </c>
-      <c r="J5" s="137">
+      <c r="J5" s="136">
         <f>'Income Statement'!I7</f>
         <v>16897</v>
       </c>
-      <c r="K5" s="137">
+      <c r="K5" s="136">
         <f>'Income Statement'!J7</f>
         <v>19126</v>
       </c>
-      <c r="L5" s="137">
+      <c r="L5" s="136">
         <f>'Income Statement'!K7</f>
         <v>24394</v>
       </c>
-      <c r="M5" s="137">
+      <c r="M5" s="136">
         <f>'Income Statement'!L7</f>
         <v>19515.2</v>
       </c>
-      <c r="N5" s="137">
+      <c r="N5" s="136">
         <f>'Income Statement'!M7</f>
         <v>20202</v>
       </c>
-      <c r="O5" s="137">
+      <c r="O5" s="136">
         <f>'Income Statement'!N7</f>
         <v>22222.2</v>
       </c>
-      <c r="P5" s="137">
+      <c r="P5" s="136">
         <f>'Income Statement'!O7</f>
         <v>24666.642000000003</v>
       </c>
-      <c r="Q5" s="137">
+      <c r="Q5" s="136">
         <f>'Income Statement'!P7</f>
         <v>27503.305830000005</v>
       </c>
@@ -16183,55 +16246,55 @@
       </c>
       <c r="C6" s="129"/>
       <c r="D6" s="131"/>
-      <c r="E6" s="138">
+      <c r="E6" s="137">
         <f>'Income Statement'!D8</f>
         <v>9.5066185318892896E-2</v>
       </c>
-      <c r="F6" s="138">
+      <c r="F6" s="137">
         <f>'Income Statement'!E8</f>
         <v>0.12807192807192808</v>
       </c>
-      <c r="G6" s="138">
+      <c r="G6" s="137">
         <f>'Income Statement'!F8</f>
         <v>9.5377258235919235E-2</v>
       </c>
-      <c r="H6" s="138">
+      <c r="H6" s="137">
         <f>'Income Statement'!G8</f>
         <v>7.931118117875334E-2</v>
       </c>
-      <c r="I6" s="138">
+      <c r="I6" s="137">
         <f>'Income Statement'!H8</f>
         <v>0.10419475655430711</v>
       </c>
-      <c r="J6" s="138">
+      <c r="J6" s="137">
         <f>'Income Statement'!I8</f>
         <v>0.14625873414286683</v>
       </c>
-      <c r="K6" s="138">
+      <c r="K6" s="137">
         <f>'Income Statement'!J8</f>
         <v>0.13191690832692193</v>
       </c>
-      <c r="L6" s="138">
+      <c r="L6" s="137">
         <f>'Income Statement'!K8</f>
         <v>0.2754365784795566</v>
       </c>
-      <c r="M6" s="138">
+      <c r="M6" s="137">
         <f>'Income Statement'!L8</f>
         <v>2.0349262783645336E-2</v>
       </c>
-      <c r="N6" s="138" t="e">
+      <c r="N6" s="137" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="O6" s="138">
+      <c r="O6" s="137">
         <f>'Income Statement'!N8</f>
         <v>0.1</v>
       </c>
-      <c r="P6" s="138">
+      <c r="P6" s="137">
         <f>'Income Statement'!O8</f>
         <v>0.11</v>
       </c>
-      <c r="Q6" s="138">
+      <c r="Q6" s="137">
         <f>'Income Statement'!P8</f>
         <v>0.11499999999999999</v>
       </c>
@@ -16243,59 +16306,59 @@
       <c r="C7" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="D7" s="139">
+      <c r="D7" s="138">
         <f>'Income Statement'!C16</f>
         <v>1850</v>
       </c>
-      <c r="E7" s="139">
+      <c r="E7" s="138">
         <f>'Income Statement'!D16</f>
         <v>2097</v>
       </c>
-      <c r="F7" s="139">
+      <c r="F7" s="138">
         <f>'Income Statement'!E16</f>
         <v>2618</v>
       </c>
-      <c r="G7" s="139">
+      <c r="G7" s="138">
         <f>'Income Statement'!F16</f>
         <v>2926</v>
       </c>
-      <c r="H7" s="139">
+      <c r="H7" s="138">
         <f>'Income Statement'!G16</f>
         <v>3202</v>
       </c>
-      <c r="I7" s="139">
+      <c r="I7" s="138">
         <f>'Income Statement'!H16</f>
         <v>3562</v>
       </c>
-      <c r="J7" s="139">
+      <c r="J7" s="138">
         <f>'Income Statement'!I16</f>
         <v>3706</v>
       </c>
-      <c r="K7" s="139">
+      <c r="K7" s="138">
         <f>'Income Statement'!J16</f>
         <v>4471</v>
       </c>
-      <c r="L7" s="139">
+      <c r="L7" s="138">
         <f>'Income Statement'!K16</f>
         <v>5843</v>
       </c>
-      <c r="M7" s="139">
+      <c r="M7" s="138">
         <f>'Income Statement'!L16</f>
         <v>4674.4000000000005</v>
       </c>
-      <c r="N7" s="139">
+      <c r="N7" s="138">
         <f>'Income Statement'!M16</f>
         <v>4771</v>
       </c>
-      <c r="O7" s="139">
+      <c r="O7" s="138">
         <f>'Income Statement'!N16</f>
         <v>4777.7730000000001</v>
       </c>
-      <c r="P7" s="139">
+      <c r="P7" s="138">
         <f>'Income Statement'!O16</f>
         <v>5426.6612400000004</v>
       </c>
-      <c r="Q7" s="139">
+      <c r="Q7" s="138">
         <f>'Income Statement'!P16</f>
         <v>6188.2438117500014</v>
       </c>
@@ -16307,59 +16370,59 @@
       <c r="C8" s="129" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="140">
+      <c r="D8" s="139">
         <f>'Income Statement'!C17</f>
         <v>0.20238485942457063</v>
       </c>
-      <c r="E8" s="140">
+      <c r="E8" s="139">
         <f>'Income Statement'!D17</f>
         <v>0.20949050949050949</v>
       </c>
-      <c r="F8" s="140">
+      <c r="F8" s="139">
         <f>'Income Statement'!E17</f>
         <v>0.23184555437477861</v>
       </c>
-      <c r="G8" s="140">
+      <c r="G8" s="139">
         <f>'Income Statement'!F17</f>
         <v>0.23655913978494625</v>
       </c>
-      <c r="H8" s="140">
+      <c r="H8" s="139">
         <f>'Income Statement'!G17</f>
         <v>0.23985018726591761</v>
       </c>
-      <c r="I8" s="140">
+      <c r="I8" s="139">
         <f>'Income Statement'!H17</f>
         <v>0.24163896614883656</v>
       </c>
-      <c r="J8" s="140">
+      <c r="J8" s="139">
         <f>'Income Statement'!I17</f>
         <v>0.21932887494821565</v>
       </c>
-      <c r="K8" s="140">
+      <c r="K8" s="139">
         <f>'Income Statement'!J17</f>
         <v>0.2337655547422357</v>
       </c>
-      <c r="L8" s="140">
+      <c r="L8" s="139">
         <f>'Income Statement'!K17</f>
         <v>0.2395261129786013</v>
       </c>
-      <c r="M8" s="140">
+      <c r="M8" s="139">
         <f>'Income Statement'!L17</f>
         <v>0.23952611297860132</v>
       </c>
-      <c r="N8" s="140">
+      <c r="N8" s="139">
         <f>'Income Statement'!M17</f>
         <v>0.23616473616473616</v>
       </c>
-      <c r="O8" s="140">
+      <c r="O8" s="139">
         <f>'Income Statement'!N17</f>
         <v>0.215</v>
       </c>
-      <c r="P8" s="140">
+      <c r="P8" s="139">
         <f>'Income Statement'!O17</f>
         <v>0.22</v>
       </c>
-      <c r="Q8" s="140">
+      <c r="Q8" s="139">
         <f>'Income Statement'!P17</f>
         <v>0.22500000000000001</v>
       </c>
@@ -16371,59 +16434,59 @@
       <c r="C9" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="D9" s="139">
+      <c r="D9" s="138">
         <f>'Income Statement'!C18</f>
         <v>354</v>
       </c>
-      <c r="E9" s="139">
+      <c r="E9" s="138">
         <f>'Income Statement'!D18</f>
         <v>342</v>
       </c>
-      <c r="F9" s="139">
+      <c r="F9" s="138">
         <f>'Income Statement'!E18</f>
         <v>336</v>
       </c>
-      <c r="G9" s="139">
+      <c r="G9" s="138">
         <f>'Income Statement'!F18</f>
         <v>370</v>
       </c>
-      <c r="H9" s="139">
+      <c r="H9" s="138">
         <f>'Income Statement'!G18</f>
         <v>370</v>
       </c>
-      <c r="I9" s="139">
+      <c r="I9" s="138">
         <f>'Income Statement'!H18</f>
         <v>391</v>
       </c>
-      <c r="J9" s="139">
+      <c r="J9" s="138">
         <f>'Income Statement'!I18</f>
         <v>403</v>
       </c>
-      <c r="K9" s="139">
+      <c r="K9" s="138">
         <f>'Income Statement'!J18</f>
         <v>429</v>
       </c>
-      <c r="L9" s="139">
+      <c r="L9" s="138">
         <f>'Income Statement'!K18</f>
         <v>568</v>
       </c>
-      <c r="M9" s="139">
+      <c r="M9" s="138">
         <f>'Income Statement'!L18</f>
         <v>454.4</v>
       </c>
-      <c r="N9" s="139">
+      <c r="N9" s="138">
         <f>'Income Statement'!M18</f>
         <v>540</v>
       </c>
-      <c r="O9" s="139">
+      <c r="O9" s="138">
         <f>'Income Statement'!N18</f>
         <v>509.08199999999999</v>
       </c>
-      <c r="P9" s="139">
+      <c r="P9" s="138">
         <f>'Income Statement'!O18</f>
         <v>625.96531200000004</v>
       </c>
-      <c r="Q9" s="139">
+      <c r="Q9" s="138">
         <f>'Income Statement'!P18</f>
         <v>742.28600338199999</v>
       </c>
@@ -16436,59 +16499,59 @@
       <c r="C10" s="129" t="s">
         <v>142</v>
       </c>
-      <c r="D10" s="137">
+      <c r="D10" s="136">
         <f>'Income Statement'!C27</f>
         <v>1001</v>
       </c>
-      <c r="E10" s="137">
+      <c r="E10" s="136">
         <f>'Income Statement'!D27</f>
         <v>1225</v>
       </c>
-      <c r="F10" s="137">
+      <c r="F10" s="136">
         <f>'Income Statement'!E27</f>
         <v>1607</v>
       </c>
-      <c r="G10" s="137">
+      <c r="G10" s="136">
         <f>'Income Statement'!F27</f>
         <v>1968</v>
       </c>
-      <c r="H10" s="137">
+      <c r="H10" s="136">
         <f>'Income Statement'!G27</f>
         <v>2082</v>
       </c>
-      <c r="I10" s="137">
+      <c r="I10" s="136">
         <f>'Income Statement'!H27</f>
         <v>2118</v>
       </c>
-      <c r="J10" s="137">
+      <c r="J10" s="136">
         <f>'Income Statement'!I27</f>
         <v>2391</v>
       </c>
-      <c r="K10" s="137">
+      <c r="K10" s="136">
         <f>'Income Statement'!J27</f>
         <v>2999</v>
       </c>
-      <c r="L10" s="137">
+      <c r="L10" s="136">
         <f>'Income Statement'!K27</f>
         <v>3933</v>
       </c>
-      <c r="M10" s="137">
+      <c r="M10" s="136">
         <f>'Income Statement'!L27</f>
         <v>3146.3999999999996</v>
       </c>
-      <c r="N10" s="137">
+      <c r="N10" s="136">
         <f>'Income Statement'!M27</f>
         <v>3314</v>
       </c>
-      <c r="O10" s="137">
+      <c r="O10" s="136">
         <f>'Income Statement'!N27</f>
         <v>3279.5080289999996</v>
       </c>
-      <c r="P10" s="137">
+      <c r="P10" s="136">
         <f>'Income Statement'!O27</f>
         <v>3705.1550043900002</v>
       </c>
-      <c r="Q10" s="137">
+      <c r="Q10" s="136">
         <f>'Income Statement'!P27</f>
         <v>4200.668307137611</v>
       </c>
@@ -16500,59 +16563,59 @@
       <c r="C11" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="141">
+      <c r="D11" s="140">
         <f>'Income Statement'!C27/'Income Statement'!C7</f>
         <v>0.1095066185318893</v>
       </c>
-      <c r="E11" s="141">
+      <c r="E11" s="140">
         <f>'Income Statement'!D27/'Income Statement'!D7</f>
         <v>0.12237762237762238</v>
       </c>
-      <c r="F11" s="141">
+      <c r="F11" s="140">
         <f>'Income Statement'!E27/'Income Statement'!E7</f>
         <v>0.14231314204746723</v>
       </c>
-      <c r="G11" s="141">
+      <c r="G11" s="140">
         <f>'Income Statement'!F27/'Income Statement'!F7</f>
         <v>0.15910744603444094</v>
       </c>
-      <c r="H11" s="141">
+      <c r="H11" s="140">
         <f>'Income Statement'!G27/'Income Statement'!G7</f>
         <v>0.15595505617977529</v>
       </c>
-      <c r="I11" s="141">
+      <c r="I11" s="140">
         <f>'Income Statement'!H27/'Income Statement'!H7</f>
         <v>0.14368089003459739</v>
       </c>
-      <c r="J11" s="141">
+      <c r="J11" s="140">
         <f>'Income Statement'!I27/'Income Statement'!I7</f>
         <v>0.14150440906669823</v>
       </c>
-      <c r="K11" s="141">
+      <c r="K11" s="140">
         <f>'Income Statement'!J27/'Income Statement'!J7</f>
         <v>0.15680225870542716</v>
       </c>
-      <c r="L11" s="141">
+      <c r="L11" s="140">
         <f>'Income Statement'!K27/'Income Statement'!K7</f>
         <v>0.16122817086168731</v>
       </c>
-      <c r="M11" s="141">
+      <c r="M11" s="140">
         <f>'Income Statement'!L27/'Income Statement'!L7</f>
         <v>0.16122817086168728</v>
       </c>
-      <c r="N11" s="141">
+      <c r="N11" s="140">
         <f>'Income Statement'!M27/'Income Statement'!M7</f>
         <v>0.16404316404316405</v>
       </c>
-      <c r="O11" s="141">
+      <c r="O11" s="140">
         <f>'Income Statement'!N27/'Income Statement'!N7</f>
         <v>0.14757800888300887</v>
       </c>
-      <c r="P11" s="141">
+      <c r="P11" s="140">
         <f>'Income Statement'!O27/'Income Statement'!O7</f>
         <v>0.15020913687359633</v>
       </c>
-      <c r="Q11" s="141">
+      <c r="Q11" s="140">
         <f>'Income Statement'!P27/'Income Statement'!P7</f>
         <v>0.15273321443982976</v>
       </c>
@@ -16564,59 +16627,59 @@
       <c r="C12" s="129" t="s">
         <v>150</v>
       </c>
-      <c r="D12" s="137">
+      <c r="D12" s="136">
         <f>'Income Statement'!C37</f>
         <v>5.19</v>
       </c>
-      <c r="E12" s="137">
+      <c r="E12" s="136">
         <f>'Income Statement'!D37</f>
         <v>6.35</v>
       </c>
-      <c r="F12" s="137">
+      <c r="F12" s="136">
         <f>'Income Statement'!E37</f>
         <v>8.33</v>
       </c>
-      <c r="G12" s="137">
+      <c r="G12" s="136">
         <f>'Income Statement'!F37</f>
         <v>10.210000000000001</v>
       </c>
-      <c r="H12" s="137">
+      <c r="H12" s="136">
         <f>'Income Statement'!G37</f>
         <v>10.8</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="136">
         <f>'Income Statement'!H37</f>
         <v>10.99</v>
       </c>
-      <c r="J12" s="137">
+      <c r="J12" s="136">
         <f>'Income Statement'!I37</f>
         <v>12.4</v>
       </c>
-      <c r="K12" s="137">
+      <c r="K12" s="136">
         <f>'Income Statement'!J37</f>
         <v>15.55</v>
       </c>
-      <c r="L12" s="137">
+      <c r="L12" s="136">
         <f>'Income Statement'!K37</f>
         <v>20.399999999999999</v>
       </c>
-      <c r="M12" s="137">
+      <c r="M12" s="136">
         <f>'Income Statement'!L37</f>
         <v>15.861000000000001</v>
       </c>
-      <c r="N12" s="137">
+      <c r="N12" s="136">
         <f>'Income Statement'!M37</f>
         <v>17.447100000000002</v>
       </c>
-      <c r="O12" s="137">
+      <c r="O12" s="136">
         <f>'Income Statement'!N37</f>
         <v>19.191810000000004</v>
       </c>
-      <c r="P12" s="137">
+      <c r="P12" s="136">
         <f>'Income Statement'!O37</f>
         <v>21.110991000000006</v>
       </c>
-      <c r="Q12" s="137">
+      <c r="Q12" s="136">
         <f>'Income Statement'!P37</f>
         <v>23.22209010000001</v>
       </c>
@@ -16628,59 +16691,59 @@
       <c r="C13" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="D13" s="139">
+      <c r="D13" s="138">
         <f>'Cash Flow'!C13</f>
         <v>1466</v>
       </c>
-      <c r="E13" s="139">
+      <c r="E13" s="138">
         <f>'Cash Flow'!D13</f>
         <v>1818</v>
       </c>
-      <c r="F13" s="139">
+      <c r="F13" s="138">
         <f>'Cash Flow'!E13</f>
         <v>2052</v>
       </c>
-      <c r="G13" s="139">
+      <c r="G13" s="138">
         <f>'Cash Flow'!F13</f>
         <v>2295</v>
       </c>
-      <c r="H13" s="139">
+      <c r="H13" s="138">
         <f>'Cash Flow'!G13</f>
         <v>2454</v>
       </c>
-      <c r="I13" s="139">
+      <c r="I13" s="138">
         <f>'Cash Flow'!H13</f>
         <v>2236</v>
       </c>
-      <c r="J13" s="139">
+      <c r="J13" s="138">
         <f>'Cash Flow'!I13</f>
         <v>2737</v>
       </c>
-      <c r="K13" s="139">
+      <c r="K13" s="138">
         <f>'Cash Flow'!J13</f>
         <v>3392</v>
       </c>
-      <c r="L13" s="139">
+      <c r="L13" s="138">
         <f>'Cash Flow'!K13</f>
         <v>4175</v>
       </c>
-      <c r="M13" s="139">
+      <c r="M13" s="138">
         <f>'Cash Flow'!L13</f>
         <v>2105.6</v>
       </c>
-      <c r="N13" s="139">
+      <c r="N13" s="138">
         <f>'Cash Flow'!M13</f>
         <v>2936</v>
       </c>
-      <c r="O13" s="139">
+      <c r="O13" s="138">
         <f>'Cash Flow'!N13</f>
         <v>2602.9218090157533</v>
       </c>
-      <c r="P13" s="139">
+      <c r="P13" s="138">
         <f>'Cash Flow'!O13</f>
         <v>3028.5425455235136</v>
       </c>
-      <c r="Q13" s="139">
+      <c r="Q13" s="138">
         <f>'Cash Flow'!P13</f>
         <v>3480.8104333328838</v>
       </c>
@@ -16692,59 +16755,59 @@
       <c r="C14" s="129" t="s">
         <v>142</v>
       </c>
-      <c r="D14" s="137">
+      <c r="D14" s="136">
         <f>-Schedules!C8</f>
         <v>-207</v>
       </c>
-      <c r="E14" s="137">
+      <c r="E14" s="136">
         <f>-Schedules!D8</f>
         <v>-199</v>
       </c>
-      <c r="F14" s="137">
+      <c r="F14" s="136">
         <f>-Schedules!E8</f>
         <v>-166</v>
       </c>
-      <c r="G14" s="137">
+      <c r="G14" s="136">
         <f>-Schedules!F8</f>
         <v>-155</v>
       </c>
-      <c r="H14" s="137">
+      <c r="H14" s="136">
         <f>-Schedules!G8</f>
         <v>-478</v>
       </c>
-      <c r="I14" s="137">
+      <c r="I14" s="136">
         <f>-Schedules!H8</f>
         <v>-735</v>
       </c>
-      <c r="J14" s="137">
+      <c r="J14" s="136">
         <f>-Schedules!I8</f>
         <v>-550</v>
       </c>
-      <c r="K14" s="137">
+      <c r="K14" s="136">
         <f>-Schedules!J8</f>
         <v>-1371</v>
       </c>
-      <c r="L14" s="137">
+      <c r="L14" s="136">
         <f>-Schedules!K8</f>
         <v>-1883</v>
       </c>
-      <c r="M14" s="137">
+      <c r="M14" s="136">
         <f>-Schedules!L8</f>
         <v>-1506.4</v>
       </c>
-      <c r="N14" s="137">
+      <c r="N14" s="136">
         <f>-Schedules!M8</f>
         <v>-2009</v>
       </c>
-      <c r="O14" s="137">
+      <c r="O14" s="136">
         <f>-Schedules!N8</f>
         <v>-1555.5540000000001</v>
       </c>
-      <c r="P14" s="137">
+      <c r="P14" s="136">
         <f>-Schedules!O8</f>
         <v>-1603.3317300000003</v>
       </c>
-      <c r="Q14" s="137">
+      <c r="Q14" s="136">
         <f>-Schedules!P8</f>
         <v>-1512.6818206500002</v>
       </c>
@@ -16756,59 +16819,59 @@
       <c r="C15" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="139">
+      <c r="D15" s="138">
         <f>'Cash Flow'!C32</f>
         <v>1353</v>
       </c>
-      <c r="E15" s="139">
+      <c r="E15" s="138">
         <f>'Cash Flow'!D32</f>
         <v>1622</v>
       </c>
-      <c r="F15" s="139">
+      <c r="F15" s="138">
         <f>'Cash Flow'!E32</f>
         <v>1890</v>
       </c>
-      <c r="G15" s="139">
+      <c r="G15" s="138">
         <f>'Cash Flow'!F32</f>
         <v>2143</v>
       </c>
-      <c r="H15" s="139">
+      <c r="H15" s="138">
         <f>'Cash Flow'!G32</f>
         <v>1980</v>
       </c>
-      <c r="I15" s="139">
+      <c r="I15" s="138">
         <f>'Cash Flow'!H32</f>
         <v>1505</v>
       </c>
-      <c r="J15" s="139">
+      <c r="J15" s="138">
         <f>'Cash Flow'!I32</f>
         <v>2197</v>
       </c>
-      <c r="K15" s="139">
+      <c r="K15" s="138">
         <f>'Cash Flow'!J32</f>
         <v>2028</v>
       </c>
-      <c r="L15" s="139">
+      <c r="L15" s="138">
         <f>'Cash Flow'!K32</f>
         <v>2296</v>
       </c>
-      <c r="M15" s="139">
+      <c r="M15" s="138">
         <f>'Cash Flow'!L32</f>
         <v>599.19999999999982</v>
       </c>
-      <c r="N15" s="139">
+      <c r="N15" s="138">
         <f>'Cash Flow'!M32</f>
         <v>932</v>
       </c>
-      <c r="O15" s="139">
+      <c r="O15" s="138">
         <f>'Cash Flow'!N32</f>
         <v>1047.3678090157532</v>
       </c>
-      <c r="P15" s="139">
+      <c r="P15" s="138">
         <f>'Cash Flow'!O32</f>
         <v>1425.2108155235132</v>
       </c>
-      <c r="Q15" s="139">
+      <c r="Q15" s="138">
         <f>'Cash Flow'!P32</f>
         <v>1968.1286126828836</v>
       </c>
@@ -16820,59 +16883,59 @@
       <c r="C16" s="129" t="s">
         <v>142</v>
       </c>
-      <c r="D16" s="137">
+      <c r="D16" s="136">
         <f>'Cash Flow'!C30</f>
         <v>880</v>
       </c>
-      <c r="E16" s="137">
+      <c r="E16" s="136">
         <f>'Cash Flow'!D30</f>
         <v>1457</v>
       </c>
-      <c r="F16" s="137">
+      <c r="F16" s="136">
         <f>'Cash Flow'!E30</f>
         <v>1610</v>
       </c>
-      <c r="G16" s="137">
+      <c r="G16" s="136">
         <f>'Cash Flow'!F30</f>
         <v>1308</v>
       </c>
-      <c r="H16" s="137">
+      <c r="H16" s="136">
         <f>'Cash Flow'!G30</f>
         <v>1770</v>
       </c>
-      <c r="I16" s="137">
+      <c r="I16" s="136">
         <f>'Cash Flow'!H30</f>
         <v>735</v>
       </c>
-      <c r="J16" s="137">
+      <c r="J16" s="136">
         <f>'Cash Flow'!I30</f>
         <v>946</v>
       </c>
-      <c r="K16" s="137">
+      <c r="K16" s="136">
         <f>'Cash Flow'!J30</f>
         <v>946</v>
       </c>
-      <c r="L16" s="137">
+      <c r="L16" s="136">
         <f>'Cash Flow'!K30</f>
         <v>779</v>
       </c>
-      <c r="M16" s="137">
+      <c r="M16" s="136">
         <f>'Cash Flow'!L30</f>
         <v>540.59999999999991</v>
       </c>
-      <c r="N16" s="137">
+      <c r="N16" s="136">
         <f>'Cash Flow'!M30</f>
         <v>96</v>
       </c>
-      <c r="O16" s="137">
+      <c r="O16" s="136">
         <f>'Cash Flow'!N30</f>
         <v>-1795.4852127342465</v>
       </c>
-      <c r="P16" s="137">
+      <c r="P16" s="136">
         <f>'Cash Flow'!O30</f>
         <v>-3592.6950786349335</v>
       </c>
-      <c r="Q16" s="137">
+      <c r="Q16" s="136">
         <f>'Cash Flow'!P30</f>
         <v>-5285.1275583021388</v>
       </c>
@@ -16884,59 +16947,59 @@
       <c r="C17" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="139">
+      <c r="D17" s="138">
         <f>'Balance Sheet'!C21</f>
         <v>6810</v>
       </c>
-      <c r="E17" s="139">
+      <c r="E17" s="138">
         <f>'Balance Sheet'!D21</f>
         <v>7363</v>
       </c>
-      <c r="F17" s="139">
+      <c r="F17" s="138">
         <f>'Balance Sheet'!E21</f>
         <v>8088</v>
       </c>
-      <c r="G17" s="139">
+      <c r="G17" s="138">
         <f>'Balance Sheet'!F21</f>
         <v>7173</v>
       </c>
-      <c r="H17" s="139">
+      <c r="H17" s="138">
         <f>'Balance Sheet'!G21</f>
         <v>7900</v>
       </c>
-      <c r="I17" s="139">
+      <c r="I17" s="138">
         <f>'Balance Sheet'!H21</f>
         <v>8234</v>
       </c>
-      <c r="J17" s="139">
+      <c r="J17" s="138">
         <f>'Balance Sheet'!I21</f>
         <v>8979</v>
       </c>
-      <c r="K17" s="139">
+      <c r="K17" s="138">
         <f>'Balance Sheet'!J21</f>
         <v>8979</v>
       </c>
-      <c r="L17" s="139">
+      <c r="L17" s="138">
         <f>'Balance Sheet'!K21</f>
         <v>10523</v>
       </c>
-      <c r="M17" s="139">
+      <c r="M17" s="138">
         <f>'Balance Sheet'!L21</f>
         <v>10565.387199999999</v>
       </c>
-      <c r="N17" s="139">
+      <c r="N17" s="138">
         <f>'Balance Sheet'!M21</f>
         <v>12324</v>
       </c>
-      <c r="O17" s="139">
+      <c r="O17" s="138">
         <f>'Balance Sheet'!N21</f>
         <v>11561.510431101371</v>
       </c>
-      <c r="P17" s="139">
+      <c r="P17" s="138">
         <f>'Balance Sheet'!O21</f>
         <v>11039.43817492671</v>
       </c>
-      <c r="Q17" s="139">
+      <c r="Q17" s="138">
         <f>'Balance Sheet'!P21</f>
         <v>10483.480672475176</v>
       </c>
@@ -16948,59 +17011,59 @@
       <c r="C18" s="129" t="s">
         <v>142</v>
       </c>
-      <c r="D18" s="137">
+      <c r="D18" s="136">
         <f>'Balance Sheet'!C30</f>
         <v>3282</v>
       </c>
-      <c r="E18" s="137">
+      <c r="E18" s="136">
         <f>'Balance Sheet'!D30</f>
         <v>3420</v>
       </c>
-      <c r="F18" s="137">
+      <c r="F18" s="136">
         <f>'Balance Sheet'!E30</f>
         <v>4117</v>
       </c>
-      <c r="G18" s="137">
+      <c r="G18" s="136">
         <f>'Balance Sheet'!F30</f>
         <v>1918</v>
       </c>
-      <c r="H18" s="137">
+      <c r="H18" s="136">
         <f>'Balance Sheet'!G30</f>
         <v>2019</v>
       </c>
-      <c r="I18" s="137">
+      <c r="I18" s="136">
         <f>'Balance Sheet'!H30</f>
         <v>1946</v>
       </c>
-      <c r="J18" s="137">
+      <c r="J18" s="136">
         <f>'Balance Sheet'!I30</f>
         <v>2459</v>
       </c>
-      <c r="K18" s="137">
+      <c r="K18" s="136">
         <f>'Balance Sheet'!J30</f>
         <v>2459</v>
       </c>
-      <c r="L18" s="137">
+      <c r="L18" s="136">
         <f>'Balance Sheet'!K30</f>
         <v>3340</v>
       </c>
-      <c r="M18" s="137">
+      <c r="M18" s="136">
         <f>'Balance Sheet'!L30</f>
         <v>4079.9999999999995</v>
       </c>
-      <c r="N18" s="137">
+      <c r="N18" s="136">
         <f>'Balance Sheet'!M30</f>
         <v>4117</v>
       </c>
-      <c r="O18" s="137">
+      <c r="O18" s="136">
         <f>'Balance Sheet'!N30</f>
         <v>4937.2970072500002</v>
       </c>
-      <c r="P18" s="137">
+      <c r="P18" s="136">
         <f>'Balance Sheet'!O30</f>
         <v>5752.4311082158001</v>
       </c>
-      <c r="Q18" s="137">
+      <c r="Q18" s="136">
         <f>'Balance Sheet'!P30</f>
         <v>6592.5647696433207</v>
       </c>
@@ -17012,59 +17075,59 @@
       <c r="C19" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="139">
+      <c r="D19" s="138">
         <f>'Balance Sheet'!C29</f>
         <v>3186</v>
       </c>
-      <c r="E19" s="139">
+      <c r="E19" s="138">
         <f>'Balance Sheet'!D29</f>
         <v>3324</v>
       </c>
-      <c r="F19" s="139">
+      <c r="F19" s="138">
         <f>'Balance Sheet'!E29</f>
         <v>4021</v>
       </c>
-      <c r="G19" s="139">
+      <c r="G19" s="138">
         <f>'Balance Sheet'!F29</f>
         <v>1822</v>
       </c>
-      <c r="H19" s="139">
+      <c r="H19" s="138">
         <f>'Balance Sheet'!G29</f>
         <v>1923</v>
       </c>
-      <c r="I19" s="139">
+      <c r="I19" s="138">
         <f>'Balance Sheet'!H29</f>
         <v>1850</v>
       </c>
-      <c r="J19" s="139">
+      <c r="J19" s="138">
         <f>'Balance Sheet'!I29</f>
         <v>2363</v>
       </c>
-      <c r="K19" s="139">
+      <c r="K19" s="138">
         <f>'Balance Sheet'!J29</f>
         <v>2363</v>
       </c>
-      <c r="L19" s="139">
+      <c r="L19" s="138">
         <f>'Balance Sheet'!K29</f>
         <v>3244</v>
       </c>
-      <c r="M19" s="139">
+      <c r="M19" s="138">
         <f>'Balance Sheet'!L29</f>
         <v>3983.9999999999995</v>
       </c>
-      <c r="N19" s="139">
+      <c r="N19" s="138">
         <f>'Balance Sheet'!M29</f>
         <v>4021</v>
       </c>
-      <c r="O19" s="139">
+      <c r="O19" s="138">
         <f>'Balance Sheet'!N29</f>
         <v>4840.8770072500001</v>
       </c>
-      <c r="P19" s="139">
+      <c r="P19" s="138">
         <f>'Balance Sheet'!O29</f>
         <v>5656.0111082158</v>
       </c>
-      <c r="Q19" s="139">
+      <c r="Q19" s="138">
         <f>'Balance Sheet'!P29</f>
         <v>6496.1447696433206</v>
       </c>
@@ -17076,59 +17139,59 @@
       <c r="C20" s="129" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="140">
+      <c r="D20" s="139">
         <f>'Income Statement'!C27/'Balance Sheet'!C30</f>
         <v>0.30499695307739183</v>
       </c>
-      <c r="E20" s="140">
+      <c r="E20" s="139">
         <f>'Income Statement'!D27/'Balance Sheet'!D30</f>
         <v>0.358187134502924</v>
       </c>
-      <c r="F20" s="140">
+      <c r="F20" s="139">
         <f>'Income Statement'!E27/'Balance Sheet'!E30</f>
         <v>0.39033276657760507</v>
       </c>
-      <c r="G20" s="140">
+      <c r="G20" s="139">
         <f>'Income Statement'!F27/'Balance Sheet'!F30</f>
         <v>1.0260688216892597</v>
       </c>
-      <c r="H20" s="140">
+      <c r="H20" s="139">
         <f>'Income Statement'!G27/'Balance Sheet'!G30</f>
         <v>1.0312035661218424</v>
       </c>
-      <c r="I20" s="138">
+      <c r="I20" s="137">
         <f>I10/I18</f>
         <v>1.0883864337101747</v>
       </c>
-      <c r="J20" s="140">
+      <c r="J20" s="139">
         <f>'Income Statement'!I27/'Balance Sheet'!I30</f>
         <v>0.97234648230988208</v>
       </c>
-      <c r="K20" s="140">
+      <c r="K20" s="139">
         <f>'Income Statement'!J27/'Balance Sheet'!J30</f>
         <v>1.2196014640097601</v>
       </c>
-      <c r="L20" s="140">
+      <c r="L20" s="139">
         <f>'Income Statement'!K27/'Balance Sheet'!K30</f>
         <v>1.1775449101796407</v>
       </c>
-      <c r="M20" s="140">
+      <c r="M20" s="139">
         <f>'Income Statement'!L27/'Balance Sheet'!L30</f>
         <v>0.77117647058823524</v>
       </c>
-      <c r="N20" s="140">
+      <c r="N20" s="139">
         <f>'Income Statement'!M27/'Balance Sheet'!M30</f>
         <v>0.80495506436725772</v>
       </c>
-      <c r="O20" s="140">
+      <c r="O20" s="139">
         <f>'Income Statement'!N27/'Balance Sheet'!N30</f>
         <v>0.66423146595886806</v>
       </c>
-      <c r="P20" s="140">
+      <c r="P20" s="139">
         <f>'Income Statement'!O27/'Balance Sheet'!O30</f>
         <v>0.64410245593348925</v>
       </c>
-      <c r="Q20" s="140">
+      <c r="Q20" s="139">
         <f>'Income Statement'!P27/'Balance Sheet'!P30</f>
         <v>0.63718271324088649</v>
       </c>
@@ -17140,59 +17203,59 @@
       <c r="C21" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="D21" s="141">
+      <c r="D21" s="140">
         <f>'Income Statement'!C19/'Balance Sheet'!C21</f>
         <v>0.21967694566813509</v>
       </c>
-      <c r="E21" s="141">
+      <c r="E21" s="140">
         <f>'Income Statement'!D19/'Balance Sheet'!D21</f>
         <v>0.23835393182126852</v>
       </c>
-      <c r="F21" s="141">
+      <c r="F21" s="140">
         <f>'Income Statement'!E19/'Balance Sheet'!E21</f>
         <v>0.28214638971315531</v>
       </c>
-      <c r="G21" s="141">
+      <c r="G21" s="140">
         <f>'Income Statement'!F19/'Balance Sheet'!F21</f>
         <v>0.35633626097866999</v>
       </c>
-      <c r="H21" s="141">
+      <c r="H21" s="140">
         <f>'Income Statement'!G19/'Balance Sheet'!G21</f>
         <v>0.35848101265822785</v>
       </c>
-      <c r="I21" s="141">
+      <c r="I21" s="140">
         <f>'Income Statement'!H19/'Balance Sheet'!H21</f>
         <v>0.38511051736701479</v>
       </c>
-      <c r="J21" s="141">
+      <c r="J21" s="140">
         <f>'Income Statement'!I19/'Balance Sheet'!I21</f>
         <v>0.36785833611760776</v>
       </c>
-      <c r="K21" s="141">
+      <c r="K21" s="140">
         <f>'Income Statement'!J19/'Balance Sheet'!J21</f>
         <v>0.45016148791624905</v>
       </c>
-      <c r="L21" s="141">
+      <c r="L21" s="140">
         <f>'Income Statement'!K19/'Balance Sheet'!K21</f>
         <v>0.50128290411479615</v>
       </c>
-      <c r="M21" s="141">
+      <c r="M21" s="140">
         <f>'Income Statement'!L19/'Balance Sheet'!L21</f>
         <v>0.39941744870457763</v>
       </c>
-      <c r="N21" s="141">
+      <c r="N21" s="140">
         <f>'Income Statement'!M19/'Balance Sheet'!M21</f>
         <v>0.34331385913664397</v>
       </c>
-      <c r="O21" s="141">
+      <c r="O21" s="140">
         <f>'Income Statement'!N19/'Balance Sheet'!N21</f>
         <v>0.36921568556621165</v>
       </c>
-      <c r="P21" s="141">
+      <c r="P21" s="140">
         <f>'Income Statement'!O19/'Balance Sheet'!O21</f>
         <v>0.43486777605255</v>
       </c>
-      <c r="Q21" s="141">
+      <c r="Q21" s="140">
         <f>'Income Statement'!P19/'Balance Sheet'!P21</f>
         <v>0.51947993023601358</v>
       </c>
@@ -17204,59 +17267,59 @@
       <c r="C22" s="129" t="s">
         <v>161</v>
       </c>
-      <c r="D22" s="142">
+      <c r="D22" s="141">
         <f>'Balance Sheet'!C16/'Income Statement'!C7*365</f>
         <v>37.534186631659558</v>
       </c>
-      <c r="E22" s="142">
+      <c r="E22" s="141">
         <f>'Balance Sheet'!D16/'Income Statement'!D7*365</f>
         <v>32.890109890109891</v>
       </c>
-      <c r="F22" s="142">
+      <c r="F22" s="141">
         <f>'Balance Sheet'!E16/'Income Statement'!E7*365</f>
         <v>31.224760892667376</v>
       </c>
-      <c r="G22" s="142">
+      <c r="G22" s="141">
         <f>'Balance Sheet'!F16/'Income Statement'!F7*365</f>
         <v>37.860376748322423</v>
       </c>
-      <c r="H22" s="142">
+      <c r="H22" s="141">
         <f>'Balance Sheet'!G16/'Income Statement'!G7*365</f>
         <v>38.714606741573036</v>
       </c>
-      <c r="I22" s="142">
+      <c r="I22" s="141">
         <f>'Balance Sheet'!H16/'Income Statement'!H7*365</f>
         <v>39.444067566650837</v>
       </c>
-      <c r="J22" s="142">
+      <c r="J22" s="141">
         <f>'Balance Sheet'!I16/'Income Statement'!I7*365</f>
         <v>41.66923122447772</v>
       </c>
-      <c r="K22" s="142">
+      <c r="K22" s="141">
         <f>'Balance Sheet'!J16/'Income Statement'!J7*365</f>
         <v>36.81297709923664</v>
       </c>
-      <c r="L22" s="142">
+      <c r="L22" s="141">
         <f>'Balance Sheet'!K16/'Income Statement'!K7*365</f>
         <v>31.257071411002705</v>
       </c>
-      <c r="M22" s="142">
+      <c r="M22" s="141">
         <f>'Balance Sheet'!L16/'Income Statement'!L7*365</f>
         <v>36.864999999999995</v>
       </c>
-      <c r="N22" s="142">
+      <c r="N22" s="141">
         <f>'Balance Sheet'!M16/'Income Statement'!M7*365</f>
         <v>51.492426492426489</v>
       </c>
-      <c r="O22" s="142">
+      <c r="O22" s="141">
         <f>'Balance Sheet'!N16/'Income Statement'!N7*365</f>
         <v>52.000000000000007</v>
       </c>
-      <c r="P22" s="142">
+      <c r="P22" s="141">
         <f>'Balance Sheet'!O16/'Income Statement'!O7*365</f>
         <v>50.999999999999993</v>
       </c>
-      <c r="Q22" s="142">
+      <c r="Q22" s="141">
         <f>'Balance Sheet'!P16/'Income Statement'!P7*365</f>
         <v>50</v>
       </c>
@@ -17268,59 +17331,59 @@
       <c r="C23" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="D23" s="143">
+      <c r="D23" s="142">
         <f>'Balance Sheet'!C17/'Income Statement'!C7*365</f>
         <v>3.9131386062794005</v>
       </c>
-      <c r="E23" s="143">
+      <c r="E23" s="142">
         <f>'Balance Sheet'!D17/'Income Statement'!D7*365</f>
         <v>3.2452547452547456</v>
       </c>
-      <c r="F23" s="143">
+      <c r="F23" s="142">
         <f>'Balance Sheet'!E17/'Income Statement'!E7*365</f>
         <v>4.0404711300035423</v>
       </c>
-      <c r="G23" s="143">
+      <c r="G23" s="142">
         <f>'Balance Sheet'!F17/'Income Statement'!F7*365</f>
         <v>3.659147869674185</v>
       </c>
-      <c r="H23" s="143">
+      <c r="H23" s="142">
         <f>'Balance Sheet'!G17/'Income Statement'!G7*365</f>
         <v>4.51123595505618</v>
       </c>
-      <c r="I23" s="143">
+      <c r="I23" s="142">
         <f>'Balance Sheet'!H17/'Income Statement'!H7*365</f>
         <v>4.1103045926327928</v>
       </c>
-      <c r="J23" s="143">
+      <c r="J23" s="142">
         <f>'Balance Sheet'!I17/'Income Statement'!I7*365</f>
         <v>4.1474818015032255</v>
       </c>
-      <c r="K23" s="143">
+      <c r="K23" s="142">
         <f>'Balance Sheet'!J17/'Income Statement'!J7*365</f>
         <v>3.66412213740458</v>
       </c>
-      <c r="L23" s="143">
+      <c r="L23" s="142">
         <f>'Balance Sheet'!K17/'Income Statement'!K7*365</f>
         <v>4.4888087234565877</v>
       </c>
-      <c r="M23" s="143">
+      <c r="M23" s="142">
         <f>'Balance Sheet'!L17/'Income Statement'!L7*365</f>
         <v>3.65</v>
       </c>
-      <c r="N23" s="143">
+      <c r="N23" s="142">
         <f>'Balance Sheet'!M17/'Income Statement'!M7*365</f>
         <v>6.558509058509058</v>
       </c>
-      <c r="O23" s="143">
+      <c r="O23" s="142">
         <f>'Balance Sheet'!N17/'Income Statement'!N7*365</f>
         <v>7</v>
       </c>
-      <c r="P23" s="143">
+      <c r="P23" s="142">
         <f>'Balance Sheet'!O17/'Income Statement'!O7*365</f>
         <v>6.9999999999999991</v>
       </c>
-      <c r="Q23" s="143">
+      <c r="Q23" s="142">
         <f>'Balance Sheet'!P17/'Income Statement'!P7*365</f>
         <v>7</v>
       </c>
@@ -17332,59 +17395,59 @@
       <c r="C24" s="129" t="s">
         <v>142</v>
       </c>
-      <c r="D24" s="144">
+      <c r="D24" s="143">
         <f>'Balance Sheet'!C43</f>
         <v>0</v>
       </c>
-      <c r="E24" s="144">
+      <c r="E24" s="143">
         <f>'Balance Sheet'!D43</f>
         <v>0</v>
       </c>
-      <c r="F24" s="144">
+      <c r="F24" s="143">
         <f>'Balance Sheet'!E43</f>
         <v>0</v>
       </c>
-      <c r="G24" s="144">
+      <c r="G24" s="143">
         <f>'Balance Sheet'!F43</f>
         <v>0</v>
       </c>
-      <c r="H24" s="144">
+      <c r="H24" s="143">
         <f>'Balance Sheet'!G43</f>
         <v>0</v>
       </c>
-      <c r="I24" s="144">
+      <c r="I24" s="143">
         <f>'Balance Sheet'!H43</f>
         <v>0</v>
       </c>
-      <c r="J24" s="144">
+      <c r="J24" s="143">
         <f>'Balance Sheet'!I43</f>
         <v>0</v>
       </c>
-      <c r="K24" s="144">
+      <c r="K24" s="143">
         <f>'Balance Sheet'!J43</f>
         <v>0</v>
       </c>
-      <c r="L24" s="144">
+      <c r="L24" s="143">
         <f>'Balance Sheet'!K43</f>
         <v>0</v>
       </c>
-      <c r="M24" s="144">
+      <c r="M24" s="143">
         <f>'Balance Sheet'!L43</f>
         <v>0</v>
       </c>
-      <c r="N24" s="144">
+      <c r="N24" s="143">
         <f>'Balance Sheet'!M43</f>
         <v>0</v>
       </c>
-      <c r="O24" s="144">
+      <c r="O24" s="143">
         <f>'Balance Sheet'!N43</f>
         <v>0</v>
       </c>
-      <c r="P24" s="144">
+      <c r="P24" s="143">
         <f>'Balance Sheet'!O43</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="144">
+      <c r="Q24" s="143">
         <f>'Balance Sheet'!P43</f>
         <v>0</v>
       </c>
@@ -17411,137 +17474,170 @@
     </row>
     <row r="28" spans="2:17" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="145">
-        <f>O10</f>
+      <c r="B29" s="144">
+        <f>'Income Statement'!N27</f>
         <v>3279.5080289999996</v>
       </c>
-      <c r="C29" s="146">
+      <c r="C29" s="145">
         <v>0.19500000000000001</v>
       </c>
-      <c r="D29" s="146">
+      <c r="D29" s="145">
         <v>0.20499999999999999</v>
       </c>
-      <c r="E29" s="146">
+      <c r="E29" s="145">
         <v>0.215</v>
       </c>
-      <c r="F29" s="146">
+      <c r="F29" s="145">
         <v>0.22500000000000001</v>
       </c>
-      <c r="G29" s="146">
+      <c r="G29" s="145">
         <v>0.23499999999999999</v>
       </c>
-      <c r="I29" s="135"/>
+      <c r="I29" s="180" t="s">
+        <v>215</v>
+      </c>
+      <c r="J29" s="181"/>
+      <c r="K29" s="181"/>
     </row>
     <row r="30" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="147">
+      <c r="B30" s="146">
         <v>0.06</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="147">
+        <f t="dataTable" ref="C30:G34" dt2D="1" dtr="1" r1="K30" r2="K31"/>
         <v>2827.3913094000004</v>
       </c>
-      <c r="D30" s="148">
+      <c r="D30" s="147">
         <v>2986.9265034000005</v>
       </c>
-      <c r="E30" s="148">
+      <c r="E30" s="147">
         <v>3146.4616974000005</v>
       </c>
-      <c r="F30" s="148">
+      <c r="F30" s="147">
         <v>3305.9968914000005</v>
       </c>
-      <c r="G30" s="148">
+      <c r="G30" s="147">
         <v>3465.5320854000001</v>
       </c>
+      <c r="I30" s="182" t="s">
+        <v>216</v>
+      </c>
+      <c r="J30" s="182"/>
+      <c r="K30" s="183">
+        <f>Assumptions!C21</f>
+        <v>0.215</v>
+      </c>
     </row>
     <row r="31" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="147">
+      <c r="B31" s="146">
         <v>0.08</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="147">
         <v>2887.8942791999998</v>
       </c>
-      <c r="D31" s="148">
+      <c r="D31" s="147">
         <v>3050.4395711999996</v>
       </c>
-      <c r="E31" s="148">
+      <c r="E31" s="147">
         <v>3212.9848631999994</v>
       </c>
-      <c r="F31" s="148">
+      <c r="F31" s="147">
         <v>3375.5301551999996</v>
       </c>
-      <c r="G31" s="148">
+      <c r="G31" s="147">
         <v>3538.0754471999999</v>
       </c>
+      <c r="I31" s="182" t="s">
+        <v>217</v>
+      </c>
+      <c r="J31" s="182"/>
+      <c r="K31" s="184">
+        <f>Assumptions!C7</f>
+        <v>0.1</v>
+      </c>
     </row>
     <row r="32" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="147">
+      <c r="B32" s="146">
         <v>0.1</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="147">
         <v>2948.3972490000006</v>
       </c>
-      <c r="D32" s="148">
+      <c r="D32" s="147">
         <v>3113.9526390000001</v>
       </c>
-      <c r="E32" s="149">
+      <c r="E32" s="148">
         <v>3279.5080289999996</v>
       </c>
-      <c r="F32" s="148">
+      <c r="F32" s="147">
         <v>3445.0634189999996</v>
       </c>
-      <c r="G32" s="148">
+      <c r="G32" s="147">
         <v>3610.6188089999996</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="147">
+      <c r="B33" s="146">
         <v>0.12</v>
       </c>
-      <c r="C33" s="148">
+      <c r="C33" s="147">
         <v>3008.9002188000009</v>
       </c>
-      <c r="D33" s="148">
+      <c r="D33" s="147">
         <v>3177.4657068000001</v>
       </c>
-      <c r="E33" s="148">
+      <c r="E33" s="147">
         <v>3346.0311947999999</v>
       </c>
-      <c r="F33" s="148">
+      <c r="F33" s="147">
         <v>3514.5966828000001</v>
       </c>
-      <c r="G33" s="148">
+      <c r="G33" s="147">
         <v>3683.1621708000002</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="147">
+      <c r="B34" s="146">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C34" s="148">
+      <c r="C34" s="147">
         <v>3069.4031886000002</v>
       </c>
-      <c r="D34" s="148">
+      <c r="D34" s="147">
         <v>3240.9787745999997</v>
       </c>
-      <c r="E34" s="148">
+      <c r="E34" s="147">
         <v>3412.5543606000001</v>
       </c>
-      <c r="F34" s="148">
+      <c r="F34" s="147">
         <v>3584.1299466</v>
       </c>
-      <c r="G34" s="148">
+      <c r="G34" s="147">
         <v>3755.7055326</v>
       </c>
     </row>
+    <row r="35" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35"/>
+      <c r="C35" s="186"/>
+      <c r="D35" s="186"/>
+      <c r="E35" s="186"/>
+      <c r="F35" s="186"/>
+      <c r="G35" s="186"/>
+    </row>
+    <row r="36" spans="2:7" s="185" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="YF7IdUs2ftp5ZfaB05WQhbEGbCHlZhOHlES6CCAzgxu05A6vPbgDGMyfT6vnXxbAWfryhiDwQ5KrDA3ggJ7ENw==" saltValue="gFODihMrguodr+L5txYNGw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uG+5s8NNlcDZjNCNW7QvweRO8EmZMUyVyU9KF/BbsRJLChp6yUpYDekIJMCSkOvMOHTCrT12AgDurOF4HeCVaw==" saltValue="QMtdhBjyGCqYLM/0n1yKNg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="65" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="34" max="16" man="1"/>
+    <brk id="36" max="16" man="1"/>
   </rowBreaks>
+  <ignoredErrors>
+    <ignoredError sqref="K30:K31" unlockedFormula="1"/>
+  </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/assets/excel/3-statement-model-nestle-india.xlsx
+++ b/assets/excel/3-statement-model-nestle-india.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anvay Document\ANVAY-PORTFOLIO-WEBSITE\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E230EE-7A5F-4626-987F-F9CE781C6997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9320544-B2B2-4529-A71A-0160EDDCF636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="657" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="657" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER" sheetId="7" r:id="rId1"/>
@@ -2791,11 +2791,35 @@
     <xf numFmtId="1" fontId="22" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="20" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="10"/>
@@ -2803,10 +2827,34 @@
     <xf numFmtId="0" fontId="38" fillId="20" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="10"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="6"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="0" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="6"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2839,33 +2887,6 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2890,33 +2911,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="6"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="6"/>
-    </xf>
+    <xf numFmtId="10" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="9" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9355,7 +9351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DA90436-8333-4931-ACD8-6891DE87A8FC}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P34"/>
@@ -9391,11 +9387,11 @@
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2" s="10"/>
-      <c r="N2" s="165" t="s">
+      <c r="N2" s="154" t="s">
         <v>173</v>
       </c>
-      <c r="O2" s="165"/>
-      <c r="P2" s="165"/>
+      <c r="O2" s="154"/>
+      <c r="P2" s="154"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F3" s="3"/>
@@ -9408,10 +9404,10 @@
       <c r="N3" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="O3" s="153">
+      <c r="O3" s="155">
         <v>1</v>
       </c>
-      <c r="P3" s="154"/>
+      <c r="P3" s="156"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F4" s="3"/>
@@ -9424,10 +9420,10 @@
       <c r="N4" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="O4" s="187">
+      <c r="O4" s="169">
         <v>46117</v>
       </c>
-      <c r="P4" s="188"/>
+      <c r="P4" s="170"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F5" s="3"/>
@@ -9440,10 +9436,10 @@
       <c r="N5" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="O5" s="153" t="s">
+      <c r="O5" s="155" t="s">
         <v>177</v>
       </c>
-      <c r="P5" s="154"/>
+      <c r="P5" s="156"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F6" s="3"/>
@@ -9458,10 +9454,10 @@
       <c r="N6" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="O6" s="166" t="s">
+      <c r="O6" s="157" t="s">
         <v>179</v>
       </c>
-      <c r="P6" s="167"/>
+      <c r="P6" s="158"/>
     </row>
     <row r="7" spans="1:16" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F7" s="3"/>
@@ -9493,24 +9489,24 @@
     </row>
     <row r="9" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:16" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B10" s="168" t="s">
+      <c r="B10" s="161" t="s">
         <v>180</v>
       </c>
-      <c r="C10" s="168"/>
-      <c r="E10" s="149" t="s">
+      <c r="C10" s="161"/>
+      <c r="E10" s="167" t="s">
         <v>198</v>
       </c>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="149"/>
-      <c r="I10" s="149"/>
-      <c r="K10" s="150" t="s">
+      <c r="F10" s="167"/>
+      <c r="G10" s="167"/>
+      <c r="H10" s="167"/>
+      <c r="I10" s="167"/>
+      <c r="K10" s="168" t="s">
         <v>199</v>
       </c>
-      <c r="L10" s="150"/>
-      <c r="M10" s="150"/>
-      <c r="N10" s="150"/>
-      <c r="O10" s="150"/>
+      <c r="L10" s="168"/>
+      <c r="M10" s="168"/>
+      <c r="N10" s="168"/>
+      <c r="O10" s="168"/>
     </row>
     <row r="11" spans="1:16" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11"/>
@@ -9527,10 +9523,10 @@
       <c r="O11"/>
     </row>
     <row r="12" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="151" t="s">
+      <c r="B12" s="159" t="s">
         <v>181</v>
       </c>
-      <c r="C12" s="152"/>
+      <c r="C12" s="160"/>
       <c r="E12"/>
       <c r="F12" t="s">
         <v>172</v>
@@ -9538,81 +9534,81 @@
       <c r="G12"/>
       <c r="H12"/>
       <c r="I12"/>
-      <c r="K12" s="169" t="s">
+      <c r="K12" s="162" t="s">
         <v>188</v>
       </c>
-      <c r="L12" s="170"/>
-      <c r="M12" s="171" t="s">
+      <c r="L12" s="163"/>
+      <c r="M12" s="164" t="s">
         <v>191</v>
       </c>
-      <c r="N12" s="172"/>
-      <c r="O12" s="173"/>
+      <c r="N12" s="165"/>
+      <c r="O12" s="166"/>
     </row>
     <row r="13" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="151" t="s">
+      <c r="B13" s="159" t="s">
         <v>182</v>
       </c>
-      <c r="C13" s="152"/>
+      <c r="C13" s="160"/>
       <c r="E13"/>
       <c r="F13" s="6"/>
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13"/>
-      <c r="K13" s="155" t="s">
+      <c r="K13" s="171" t="s">
         <v>189</v>
       </c>
-      <c r="L13" s="156"/>
-      <c r="M13" s="159" t="s">
+      <c r="L13" s="172"/>
+      <c r="M13" s="175" t="s">
         <v>192</v>
       </c>
-      <c r="N13" s="160"/>
-      <c r="O13" s="161"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="177"/>
     </row>
     <row r="14" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="151" t="s">
+      <c r="B14" s="159" t="s">
         <v>183</v>
       </c>
-      <c r="C14" s="152"/>
+      <c r="C14" s="160"/>
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14"/>
       <c r="H14"/>
       <c r="I14"/>
-      <c r="K14" s="155" t="s">
+      <c r="K14" s="171" t="s">
         <v>194</v>
       </c>
-      <c r="L14" s="156"/>
-      <c r="M14" s="159" t="s">
+      <c r="L14" s="172"/>
+      <c r="M14" s="175" t="s">
         <v>193</v>
       </c>
-      <c r="N14" s="160"/>
-      <c r="O14" s="161"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="177"/>
     </row>
     <row r="15" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="151" t="s">
+      <c r="B15" s="159" t="s">
         <v>184</v>
       </c>
-      <c r="C15" s="152"/>
+      <c r="C15" s="160"/>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15"/>
       <c r="I15"/>
-      <c r="K15" s="157" t="s">
+      <c r="K15" s="173" t="s">
         <v>190</v>
       </c>
-      <c r="L15" s="158"/>
-      <c r="M15" s="162" t="s">
+      <c r="L15" s="174"/>
+      <c r="M15" s="178" t="s">
         <v>195</v>
       </c>
-      <c r="N15" s="163"/>
-      <c r="O15" s="164"/>
+      <c r="N15" s="179"/>
+      <c r="O15" s="180"/>
     </row>
     <row r="16" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="151" t="s">
+      <c r="B16" s="159" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="152"/>
+      <c r="C16" s="160"/>
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16"/>
@@ -9622,10 +9618,10 @@
       <c r="O16" s="5"/>
     </row>
     <row r="17" spans="2:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="151" t="s">
+      <c r="B17" s="159" t="s">
         <v>186</v>
       </c>
-      <c r="C17" s="152"/>
+      <c r="C17" s="160"/>
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17"/>
@@ -9633,10 +9629,10 @@
       <c r="I17"/>
     </row>
     <row r="18" spans="2:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="151" t="s">
+      <c r="B18" s="159" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="152"/>
+      <c r="C18" s="160"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -9652,13 +9648,13 @@
       <c r="G19"/>
     </row>
     <row r="20" spans="2:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="149" t="s">
+      <c r="B20" s="167" t="s">
         <v>200</v>
       </c>
-      <c r="C20" s="149"/>
-      <c r="D20" s="149"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="149"/>
+      <c r="C20" s="167"/>
+      <c r="D20" s="167"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
       <c r="G20"/>
     </row>
     <row r="21" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9727,14 +9723,6 @@
     <row r="34" s="2" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:O12"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="E10:I10"/>
     <mergeCell ref="K10:O10"/>
@@ -9751,6 +9739,14 @@
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="M14:O14"/>
     <mergeCell ref="M15:O15"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:O12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B12:C12" location="COVER!A1" display="1.  Cover Page" xr:uid="{C3FFABC6-12B2-4A48-8C61-D8BAB7B99ADA}"/>
@@ -9769,7 +9765,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <tabColor rgb="FFC9A84C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -9785,20 +9781,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="176" t="s">
+      <c r="B1" s="183" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
     </row>
     <row r="3" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="177" t="s">
+      <c r="B3" s="184" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
       <c r="G3" s="23"/>
     </row>
     <row r="4" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -9861,12 +9857,12 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="177" t="s">
+      <c r="B9" s="184" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="177"/>
-      <c r="D9" s="177"/>
-      <c r="E9" s="177"/>
+      <c r="C9" s="184"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
     </row>
     <row r="10" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="24" t="s">
@@ -10080,12 +10076,12 @@
       </c>
     </row>
     <row r="33" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="177" t="s">
+      <c r="B33" s="184" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="177"/>
-      <c r="D33" s="177"/>
-      <c r="E33" s="177"/>
+      <c r="C33" s="184"/>
+      <c r="D33" s="184"/>
+      <c r="E33" s="184"/>
     </row>
     <row r="34" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="24" t="s">
@@ -10238,12 +10234,12 @@
       <c r="U45" s="2"/>
     </row>
     <row r="46" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="177" t="s">
+      <c r="B46" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="177"/>
-      <c r="D46" s="177"/>
-      <c r="E46" s="177"/>
+      <c r="C46" s="184"/>
+      <c r="D46" s="184"/>
+      <c r="E46" s="184"/>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
@@ -10256,11 +10252,11 @@
       <c r="B47" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="175" t="s">
+      <c r="C47" s="182" t="s">
         <v>210</v>
       </c>
-      <c r="D47" s="175"/>
-      <c r="E47" s="175"/>
+      <c r="D47" s="182"/>
+      <c r="E47" s="182"/>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
@@ -10273,11 +10269,11 @@
       <c r="B48" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="174" t="s">
+      <c r="C48" s="181" t="s">
         <v>211</v>
       </c>
-      <c r="D48" s="174"/>
-      <c r="E48" s="174"/>
+      <c r="D48" s="181"/>
+      <c r="E48" s="181"/>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
@@ -10290,11 +10286,11 @@
       <c r="B49" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="175" t="s">
+      <c r="C49" s="182" t="s">
         <v>212</v>
       </c>
-      <c r="D49" s="175"/>
-      <c r="E49" s="175"/>
+      <c r="D49" s="182"/>
+      <c r="E49" s="182"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
@@ -10307,11 +10303,11 @@
       <c r="B50" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C50" s="174" t="s">
+      <c r="C50" s="181" t="s">
         <v>213</v>
       </c>
-      <c r="D50" s="174"/>
-      <c r="E50" s="174"/>
+      <c r="D50" s="181"/>
+      <c r="E50" s="181"/>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
@@ -10324,11 +10320,11 @@
       <c r="B51" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="C51" s="175" t="s">
+      <c r="C51" s="182" t="s">
         <v>214</v>
       </c>
-      <c r="D51" s="175"/>
-      <c r="E51" s="175"/>
+      <c r="D51" s="182"/>
+      <c r="E51" s="182"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="btk0e6SVhRA7sfinWwGdN3VUCE9wxnbs60p4s+RweUP3QlIdpvuICzRzEHwVO3nQN1v6UIt7VFJGi4LZ/K4yZw==" saltValue="bo7zv8VMBttWtlDZjbqTlQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -10356,7 +10352,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet3">
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10373,44 +10369,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:25" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="176" t="s">
+      <c r="B1" s="183" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="176"/>
-      <c r="K1" s="176"/>
-      <c r="L1" s="176"/>
-      <c r="M1" s="176"/>
-      <c r="N1" s="176"/>
-      <c r="O1" s="176"/>
-      <c r="P1" s="176"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
     </row>
     <row r="2" spans="2:25" s="2" customFormat="1" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="178" t="s">
+      <c r="C3" s="185" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="178"/>
-      <c r="J3" s="178"/>
-      <c r="K3" s="178"/>
-      <c r="L3" s="178"/>
-      <c r="M3" s="178"/>
-      <c r="N3" s="179" t="s">
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="179"/>
-      <c r="P3" s="179"/>
+      <c r="O3" s="186"/>
+      <c r="P3" s="186"/>
     </row>
     <row r="4" spans="2:25" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="46" t="s">
@@ -12001,7 +11997,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet4">
     <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -12018,44 +12014,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="176" t="s">
+      <c r="B1" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="176"/>
-      <c r="K1" s="176"/>
-      <c r="L1" s="176"/>
-      <c r="M1" s="176"/>
-      <c r="N1" s="176"/>
-      <c r="O1" s="176"/>
-      <c r="P1" s="176"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
     </row>
     <row r="2" spans="2:16" s="2" customFormat="1" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="178" t="s">
+      <c r="C3" s="185" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="178"/>
-      <c r="J3" s="178"/>
-      <c r="K3" s="178"/>
-      <c r="L3" s="178"/>
-      <c r="M3" s="178"/>
-      <c r="N3" s="179" t="s">
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="179"/>
-      <c r="P3" s="179"/>
+      <c r="O3" s="186"/>
+      <c r="P3" s="186"/>
     </row>
     <row r="4" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="46" t="s">
@@ -13203,7 +13199,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet5">
     <tabColor rgb="FF375623"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -13220,44 +13216,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="176" t="s">
+      <c r="B1" s="183" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="176"/>
-      <c r="K1" s="176"/>
-      <c r="L1" s="176"/>
-      <c r="M1" s="176"/>
-      <c r="N1" s="176"/>
-      <c r="O1" s="176"/>
-      <c r="P1" s="176"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
     </row>
     <row r="2" spans="2:16" s="2" customFormat="1" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="178" t="s">
+      <c r="C3" s="185" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="178"/>
-      <c r="J3" s="178"/>
-      <c r="K3" s="178"/>
-      <c r="L3" s="178"/>
-      <c r="M3" s="178"/>
-      <c r="N3" s="179" t="s">
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="179"/>
-      <c r="P3" s="179"/>
+      <c r="O3" s="186"/>
+      <c r="P3" s="186"/>
     </row>
     <row r="4" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="46" t="s">
@@ -14753,7 +14749,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet6">
     <tabColor rgb="FFC55A11"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -14769,44 +14765,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="176" t="s">
+      <c r="B1" s="183" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="176"/>
-      <c r="K1" s="176"/>
-      <c r="L1" s="176"/>
-      <c r="M1" s="176"/>
-      <c r="N1" s="176"/>
-      <c r="O1" s="176"/>
-      <c r="P1" s="176"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
     </row>
     <row r="2" spans="2:16" s="2" customFormat="1" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="178" t="s">
+      <c r="C3" s="185" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="178"/>
-      <c r="J3" s="178"/>
-      <c r="K3" s="178"/>
-      <c r="L3" s="178"/>
-      <c r="M3" s="178"/>
-      <c r="N3" s="179" t="s">
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="179"/>
-      <c r="P3" s="179"/>
+      <c r="O3" s="186"/>
+      <c r="P3" s="186"/>
     </row>
     <row r="4" spans="2:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="46" t="s">
@@ -16055,7 +16051,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet7">
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -16073,24 +16069,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="176" t="s">
+      <c r="B1" s="183" t="s">
         <v>137</v>
       </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="176"/>
-      <c r="K1" s="176"/>
-      <c r="L1" s="176"/>
-      <c r="M1" s="176"/>
-      <c r="N1" s="176"/>
-      <c r="O1" s="176"/>
-      <c r="P1" s="176"/>
-      <c r="Q1" s="176"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
+      <c r="Q1" s="183"/>
     </row>
     <row r="2" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17493,11 +17489,11 @@
       <c r="G29" s="145">
         <v>0.23499999999999999</v>
       </c>
-      <c r="I29" s="180" t="s">
+      <c r="I29" s="149" t="s">
         <v>215</v>
       </c>
-      <c r="J29" s="181"/>
-      <c r="K29" s="181"/>
+      <c r="J29" s="150"/>
+      <c r="K29" s="150"/>
     </row>
     <row r="30" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="146">
@@ -17519,11 +17515,11 @@
       <c r="G30" s="147">
         <v>3465.5320854000001</v>
       </c>
-      <c r="I30" s="182" t="s">
+      <c r="I30" s="151" t="s">
         <v>216</v>
       </c>
-      <c r="J30" s="182"/>
-      <c r="K30" s="183">
+      <c r="J30" s="151"/>
+      <c r="K30" s="187">
         <f>Assumptions!C21</f>
         <v>0.215</v>
       </c>
@@ -17547,11 +17543,11 @@
       <c r="G31" s="147">
         <v>3538.0754471999999</v>
       </c>
-      <c r="I31" s="182" t="s">
+      <c r="I31" s="151" t="s">
         <v>217</v>
       </c>
-      <c r="J31" s="182"/>
-      <c r="K31" s="184">
+      <c r="J31" s="151"/>
+      <c r="K31" s="188">
         <f>Assumptions!C7</f>
         <v>0.1</v>
       </c>
@@ -17618,15 +17614,15 @@
     </row>
     <row r="35" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35"/>
-      <c r="C35" s="186"/>
-      <c r="D35" s="186"/>
-      <c r="E35" s="186"/>
-      <c r="F35" s="186"/>
-      <c r="G35" s="186"/>
-    </row>
-    <row r="36" spans="2:7" s="185" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="153"/>
+      <c r="E35" s="153"/>
+      <c r="F35" s="153"/>
+      <c r="G35" s="153"/>
+    </row>
+    <row r="36" spans="2:7" s="152" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="uG+5s8NNlcDZjNCNW7QvweRO8EmZMUyVyU9KF/BbsRJLChp6yUpYDekIJMCSkOvMOHTCrT12AgDurOF4HeCVaw==" saltValue="QMtdhBjyGCqYLM/0n1yKNg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UFiF6NFsFo0qkn22/QbAAhc1avR+2DEcTvho40fMkgrwa96h0KcprCzgHjGgw7OMSYgnXvG4ux3tzH+s4e68mg==" saltValue="8CInaxQO1V740iTxYgVBcg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B1:Q1"/>
   </mergeCells>
